--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MISSISSIPPI_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MISSISSIPPI_2010.xlsx
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C82">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C476">
